--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_130/per_file_predictions_epoch_130.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run9/epoch_130/per_file_predictions_epoch_130.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="523">
   <si>
     <t>Filename</t>
   </si>
@@ -808,775 +808,781 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0,0,1,1</t>
-  </si>
-  <si>
-    <t>0.7589,0.0130,0.0680,0.1599</t>
-  </si>
-  <si>
-    <t>0.0135,0.0003,0.0004,0.9963</t>
-  </si>
-  <si>
-    <t>0.7371,0.0586,0.0051,0.1233</t>
-  </si>
-  <si>
-    <t>0.0438,0.0071,0.0035,0.9827</t>
-  </si>
-  <si>
-    <t>0.9978,0.0008,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0019,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9919,0.0033,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9955,0.0019,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9908,0.0029,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.9888,0.0163,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9968,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9940,0.0014,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.5764,0.0904,0.4533,0.0175</t>
-  </si>
-  <si>
-    <t>0.3169,0.0232,0.7994,0.0027</t>
-  </si>
-  <si>
-    <t>0.0931,0.0303,0.9225,0.0018</t>
-  </si>
-  <si>
-    <t>0.1324,0.0320,0.8723,0.0151</t>
-  </si>
-  <si>
-    <t>0.8836,0.0124,0.0540,0.0247</t>
-  </si>
-  <si>
-    <t>0.0628,0.9333,0.0041,0.0021</t>
-  </si>
-  <si>
-    <t>0.0356,0.9604,0.0037,0.0013</t>
-  </si>
-  <si>
-    <t>0.5784,0.5467,0.0093,0.0035</t>
-  </si>
-  <si>
-    <t>0.1262,0.8939,0.0033,0.0035</t>
-  </si>
-  <si>
-    <t>0.0214,0.9655,0.0085,0.0013</t>
-  </si>
-  <si>
-    <t>0.7445,0.0071,0.1524,0.0835</t>
-  </si>
-  <si>
-    <t>0.3328,0.0406,0.6178,0.0816</t>
-  </si>
-  <si>
-    <t>0.0267,0.0106,0.9587,0.0061</t>
-  </si>
-  <si>
-    <t>0.4321,0.0010,0.6604,0.0212</t>
-  </si>
-  <si>
-    <t>0.0930,0.0089,0.9435,0.0042</t>
-  </si>
-  <si>
-    <t>0.0856,0.0081,0.9354,0.0060</t>
-  </si>
-  <si>
-    <t>0.0008,0.0006,0.9920,0.0270</t>
-  </si>
-  <si>
-    <t>0.4362,0.6346,0.0198,0.0109</t>
-  </si>
-  <si>
-    <t>0.6521,0.2889,0.1033,0.0141</t>
-  </si>
-  <si>
-    <t>0.0034,0.0087,0.9843,0.0164</t>
-  </si>
-  <si>
-    <t>0.0324,0.9082,0.1272,0.0015</t>
-  </si>
-  <si>
-    <t>0.8666,0.1117,0.0212,0.0061</t>
-  </si>
-  <si>
-    <t>0.4617,0.2390,0.3589,0.0085</t>
-  </si>
-  <si>
-    <t>0.6888,0.4217,0.0088,0.0009</t>
-  </si>
-  <si>
-    <t>0.0729,0.8607,0.2358,0.0043</t>
-  </si>
-  <si>
-    <t>0.0282,0.5141,0.5316,0.0870</t>
-  </si>
-  <si>
-    <t>0.1183,0.2341,0.7438,0.0417</t>
-  </si>
-  <si>
-    <t>0.0079,0.0760,0.9476,0.0211</t>
-  </si>
-  <si>
-    <t>0.0294,0.0044,0.9677,0.0096</t>
-  </si>
-  <si>
-    <t>0.4010,0.0226,0.6843,0.0042</t>
-  </si>
-  <si>
-    <t>0.0041,0.8102,0.8089,0.0012</t>
-  </si>
-  <si>
-    <t>0.0114,0.0176,0.9619,0.0228</t>
-  </si>
-  <si>
-    <t>0.2777,0.2700,0.0688,0.6908</t>
-  </si>
-  <si>
-    <t>0.0037,0.9698,0.0106,0.0447</t>
-  </si>
-  <si>
-    <t>0.0350,0.8845,0.3232,0.0122</t>
-  </si>
-  <si>
-    <t>0.0060,0.9695,0.0124,0.0169</t>
-  </si>
-  <si>
-    <t>0.0029,0.0302,0.9726,0.0183</t>
-  </si>
-  <si>
-    <t>0.0029,0.0547,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.0542,0.0060,0.9318,0.0384</t>
-  </si>
-  <si>
-    <t>0.0331,0.0032,0.9734,0.0055</t>
-  </si>
-  <si>
-    <t>0.0042,0.0097,0.9871,0.0061</t>
-  </si>
-  <si>
-    <t>0.0066,0.0230,0.9864,0.0012</t>
-  </si>
-  <si>
-    <t>0.9399,0.0504,0.0026,0.0055</t>
-  </si>
-  <si>
-    <t>0.9259,0.0634,0.0130,0.0051</t>
-  </si>
-  <si>
-    <t>0.9681,0.0153,0.0178,0.0016</t>
-  </si>
-  <si>
-    <t>0.0073,0.0280,0.9835,0.0042</t>
-  </si>
-  <si>
-    <t>0.9830,0.0030,0.0002,0.0038</t>
-  </si>
-  <si>
-    <t>0.9878,0.0056,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9522,0.0495,0.0028,0.0022</t>
-  </si>
-  <si>
-    <t>0.0026,0.6424,0.9626,0.0009</t>
-  </si>
-  <si>
-    <t>0.0074,0.0193,0.9895,0.0013</t>
-  </si>
-  <si>
-    <t>0.0164,0.0172,0.9522,0.0285</t>
-  </si>
-  <si>
-    <t>0.0008,0.8132,0.9640,0.0002</t>
-  </si>
-  <si>
-    <t>0.0010,0.0043,0.9965,0.0014</t>
-  </si>
-  <si>
-    <t>0.0891,0.7829,0.1792,0.0024</t>
-  </si>
-  <si>
-    <t>0.0209,0.9585,0.0148,0.0028</t>
-  </si>
-  <si>
-    <t>0.8712,0.0332,0.1184,0.0149</t>
-  </si>
-  <si>
-    <t>0.7589,0.0253,0.3166,0.0078</t>
-  </si>
-  <si>
-    <t>0.0057,0.0128,0.9923,0.0016</t>
-  </si>
-  <si>
-    <t>0.0070,0.8957,0.7095,0.0023</t>
-  </si>
-  <si>
-    <t>0.0010,0.8770,0.9082,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9604,0.9029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0161,0.7293,0.8027,0.0118</t>
-  </si>
-  <si>
-    <t>0.1200,0.0008,0.0031,0.9547</t>
-  </si>
-  <si>
-    <t>0.0074,0.0083,0.0020,0.9951</t>
-  </si>
-  <si>
-    <t>0.0062,0.0017,0.0002,0.9979</t>
-  </si>
-  <si>
-    <t>0.0445,0.0061,0.0290,0.9568</t>
-  </si>
-  <si>
-    <t>0.0837,0.0065,0.0082,0.9610</t>
-  </si>
-  <si>
-    <t>0.0025,0.0100,0.0044,0.9965</t>
-  </si>
-  <si>
-    <t>0.0029,0.8999,0.5712,0.0049</t>
-  </si>
-  <si>
-    <t>0.0015,0.7735,0.9595,0.0004</t>
-  </si>
-  <si>
-    <t>0.0286,0.7515,0.2348,0.0829</t>
-  </si>
-  <si>
-    <t>0.0725,0.2337,0.7538,0.0042</t>
-  </si>
-  <si>
-    <t>0.0022,0.9140,0.7772,0.0004</t>
-  </si>
-  <si>
-    <t>0.0220,0.3700,0.8152,0.0057</t>
-  </si>
-  <si>
-    <t>0.9936,0.0018,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9917,0.0048,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9887,0.0075,0.0010,0.0005</t>
-  </si>
-  <si>
-    <t>0.9938,0.0021,0.0006,0.0005</t>
-  </si>
-  <si>
-    <t>0.9895,0.0033,0.0003,0.0011</t>
+    <t>0.7794,0.0346,0.0243,0.1579</t>
+  </si>
+  <si>
+    <t>0.0423,0.0002,0.0010,0.9883</t>
+  </si>
+  <si>
+    <t>0.3749,0.1159,0.0050,0.5312</t>
+  </si>
+  <si>
+    <t>0.2116,0.0038,0.0057,0.9113</t>
+  </si>
+  <si>
+    <t>0.9973,0.0005,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9939,0.0043,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9936,0.0018,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.9939,0.0019,0.0012,0.0007</t>
+  </si>
+  <si>
+    <t>0.9873,0.0099,0.0013,0.0005</t>
+  </si>
+  <si>
+    <t>0.9832,0.0089,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9970,0.0017,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9863,0.0033,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.6718,0.1806,0.1007,0.0559</t>
+  </si>
+  <si>
+    <t>0.1595,0.0370,0.8380,0.0051</t>
+  </si>
+  <si>
+    <t>0.3490,0.0159,0.7796,0.0052</t>
+  </si>
+  <si>
+    <t>0.1659,0.1241,0.6903,0.0028</t>
+  </si>
+  <si>
+    <t>0.8369,0.0453,0.1232,0.0124</t>
+  </si>
+  <si>
+    <t>0.0367,0.9551,0.0065,0.0017</t>
+  </si>
+  <si>
+    <t>0.1293,0.8980,0.0047,0.0022</t>
+  </si>
+  <si>
+    <t>0.5848,0.5340,0.0138,0.0011</t>
+  </si>
+  <si>
+    <t>0.2077,0.8356,0.0093,0.0016</t>
+  </si>
+  <si>
+    <t>0.0578,0.9313,0.0091,0.0036</t>
+  </si>
+  <si>
+    <t>0.4701,0.0248,0.4501,0.0973</t>
+  </si>
+  <si>
+    <t>0.5347,0.0447,0.5493,0.0319</t>
+  </si>
+  <si>
+    <t>0.0372,0.0317,0.9254,0.0164</t>
+  </si>
+  <si>
+    <t>0.2158,0.0147,0.8422,0.0099</t>
+  </si>
+  <si>
+    <t>0.1253,0.0122,0.9109,0.0053</t>
+  </si>
+  <si>
+    <t>0.0318,0.0052,0.9551,0.0302</t>
+  </si>
+  <si>
+    <t>0.0010,0.0021,0.9884,0.0295</t>
+  </si>
+  <si>
+    <t>0.6650,0.3973,0.0299,0.0097</t>
+  </si>
+  <si>
+    <t>0.4323,0.0391,0.6603,0.0328</t>
+  </si>
+  <si>
+    <t>0.0020,0.0121,0.9875,0.0048</t>
+  </si>
+  <si>
+    <t>0.0734,0.7114,0.3012,0.0011</t>
+  </si>
+  <si>
+    <t>0.3737,0.3527,0.0116,0.2288</t>
+  </si>
+  <si>
+    <t>0.3637,0.1452,0.5427,0.0029</t>
+  </si>
+  <si>
+    <t>0.5090,0.5646,0.0150,0.0023</t>
+  </si>
+  <si>
+    <t>0.2282,0.7241,0.0833,0.0196</t>
+  </si>
+  <si>
+    <t>0.0531,0.3699,0.7015,0.0339</t>
+  </si>
+  <si>
+    <t>0.0228,0.0158,0.9504,0.0259</t>
+  </si>
+  <si>
+    <t>0.0548,0.3638,0.8432,0.0270</t>
+  </si>
+  <si>
+    <t>0.0161,0.0671,0.9002,0.0704</t>
+  </si>
+  <si>
+    <t>0.0730,0.1114,0.8134,0.0173</t>
+  </si>
+  <si>
+    <t>0.0379,0.5896,0.5571,0.0038</t>
+  </si>
+  <si>
+    <t>0.0051,0.0219,0.9878,0.0008</t>
+  </si>
+  <si>
+    <t>0.6271,0.1815,0.0345,0.1202</t>
+  </si>
+  <si>
+    <t>0.0119,0.9479,0.0129,0.0504</t>
+  </si>
+  <si>
+    <t>0.0059,0.9570,0.1640,0.0021</t>
+  </si>
+  <si>
+    <t>0.0022,0.9812,0.0107,0.0198</t>
+  </si>
+  <si>
+    <t>0.0083,0.0404,0.9609,0.0182</t>
+  </si>
+  <si>
+    <t>0.0029,0.5484,0.9467,0.0006</t>
+  </si>
+  <si>
+    <t>0.1518,0.0057,0.7596,0.1578</t>
+  </si>
+  <si>
+    <t>0.1386,0.0107,0.8963,0.0059</t>
+  </si>
+  <si>
+    <t>0.0025,0.0467,0.9887,0.0018</t>
+  </si>
+  <si>
+    <t>0.0577,0.0742,0.9145,0.0055</t>
+  </si>
+  <si>
+    <t>0.8871,0.1427,0.0077,0.0026</t>
+  </si>
+  <si>
+    <t>0.9712,0.0119,0.0037,0.0036</t>
+  </si>
+  <si>
+    <t>0.9675,0.0192,0.0017,0.0031</t>
+  </si>
+  <si>
+    <t>0.0059,0.0078,0.9839,0.0215</t>
+  </si>
+  <si>
+    <t>0.9867,0.0050,0.0004,0.0014</t>
+  </si>
+  <si>
+    <t>0.9897,0.0037,0.0001,0.0011</t>
+  </si>
+  <si>
+    <t>0.9784,0.0298,0.0040,0.0003</t>
+  </si>
+  <si>
+    <t>0.0005,0.9055,0.9421,0.0003</t>
+  </si>
+  <si>
+    <t>0.0266,0.0880,0.9637,0.0026</t>
+  </si>
+  <si>
+    <t>0.0345,0.0107,0.9493,0.0151</t>
+  </si>
+  <si>
+    <t>0.0014,0.7244,0.9492,0.0003</t>
+  </si>
+  <si>
+    <t>0.0011,0.0038,0.9947,0.0026</t>
+  </si>
+  <si>
+    <t>0.0759,0.8900,0.0410,0.0068</t>
+  </si>
+  <si>
+    <t>0.0935,0.9279,0.0055,0.0011</t>
+  </si>
+  <si>
+    <t>0.6826,0.0255,0.4766,0.0050</t>
+  </si>
+  <si>
+    <t>0.8252,0.0823,0.0816,0.0229</t>
+  </si>
+  <si>
+    <t>0.0012,0.0103,0.9957,0.0014</t>
+  </si>
+  <si>
+    <t>0.0015,0.9142,0.7600,0.0002</t>
+  </si>
+  <si>
+    <t>0.0043,0.8283,0.8272,0.0008</t>
+  </si>
+  <si>
+    <t>0.0006,0.9851,0.2535,0.0012</t>
+  </si>
+  <si>
+    <t>0.0002,0.7907,0.9914,0.0001</t>
+  </si>
+  <si>
+    <t>0.1220,0.0009,0.0074,0.9405</t>
+  </si>
+  <si>
+    <t>0.0011,0.0107,0.0007,0.9988</t>
+  </si>
+  <si>
+    <t>0.0018,0.0034,0.0030,0.9976</t>
+  </si>
+  <si>
+    <t>0.0039,0.0118,0.0013,0.9966</t>
+  </si>
+  <si>
+    <t>0.0187,0.0008,0.0201,0.9796</t>
+  </si>
+  <si>
+    <t>0.0204,0.0086,0.0015,0.9913</t>
+  </si>
+  <si>
+    <t>0.0016,0.9077,0.9148,0.0005</t>
+  </si>
+  <si>
+    <t>0.0008,0.8730,0.9424,0.0001</t>
+  </si>
+  <si>
+    <t>0.0104,0.8941,0.2939,0.0029</t>
+  </si>
+  <si>
+    <t>0.0048,0.4665,0.9616,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.9270,0.9596,0.0000</t>
+  </si>
+  <si>
+    <t>0.0306,0.6711,0.6722,0.0076</t>
+  </si>
+  <si>
+    <t>0.9863,0.0067,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9793,0.0239,0.0035,0.0003</t>
+  </si>
+  <si>
+    <t>0.9872,0.0118,0.0010,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0025,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9927,0.0022,0.0004,0.0007</t>
+  </si>
+  <si>
+    <t>0.9950,0.0006,0.0002,0.0011</t>
+  </si>
+  <si>
+    <t>0.9907,0.0046,0.0010,0.0006</t>
+  </si>
+  <si>
+    <t>0.9799,0.0080,0.0056,0.0019</t>
+  </si>
+  <si>
+    <t>0.9969,0.0003,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9940,0.0043,0.0013,0.0001</t>
+  </si>
+  <si>
+    <t>0.9963,0.0007,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0022,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.9931,0.0011,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9937,0.0039,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9905,0.0014,0.0007,0.0022</t>
+  </si>
+  <si>
+    <t>0.9900,0.0040,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.0245,0.0036,0.9788,0.0058</t>
+  </si>
+  <si>
+    <t>0.0526,0.0101,0.9435,0.0121</t>
+  </si>
+  <si>
+    <t>0.8779,0.0032,0.0367,0.0400</t>
+  </si>
+  <si>
+    <t>0.0597,0.0092,0.9397,0.0149</t>
+  </si>
+  <si>
+    <t>0.1987,0.8303,0.0049,0.0043</t>
+  </si>
+  <si>
+    <t>0.0150,0.9769,0.0024,0.0007</t>
+  </si>
+  <si>
+    <t>0.4718,0.6489,0.0038,0.0030</t>
+  </si>
+  <si>
+    <t>0.1080,0.8772,0.0012,0.0048</t>
+  </si>
+  <si>
+    <t>0.0527,0.9412,0.0038,0.0018</t>
+  </si>
+  <si>
+    <t>0.0375,0.9592,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.6836,0.4477,0.0040,0.0022</t>
+  </si>
+  <si>
+    <t>0.6061,0.2475,0.2088,0.0906</t>
+  </si>
+  <si>
+    <t>0.4641,0.0202,0.7001,0.0071</t>
+  </si>
+  <si>
+    <t>0.6610,0.1756,0.1099,0.0524</t>
+  </si>
+  <si>
+    <t>0.8200,0.0388,0.1001,0.0370</t>
+  </si>
+  <si>
+    <t>0.0596,0.5935,0.0550,0.8384</t>
+  </si>
+  <si>
+    <t>0.0055,0.9803,0.0201,0.0049</t>
+  </si>
+  <si>
+    <t>0.0192,0.9217,0.2099,0.0136</t>
+  </si>
+  <si>
+    <t>0.0983,0.8079,0.1070,0.0891</t>
+  </si>
+  <si>
+    <t>0.0012,0.9175,0.9176,0.0004</t>
+  </si>
+  <si>
+    <t>0.1694,0.7542,0.1876,0.0022</t>
+  </si>
+  <si>
+    <t>0.4612,0.6086,0.0202,0.0013</t>
+  </si>
+  <si>
+    <t>0.5631,0.5753,0.0038,0.0019</t>
+  </si>
+  <si>
+    <t>0.9793,0.0138,0.0066,0.0011</t>
+  </si>
+  <si>
+    <t>0.9767,0.0098,0.0031,0.0028</t>
+  </si>
+  <si>
+    <t>0.9902,0.0013,0.0006,0.0020</t>
+  </si>
+  <si>
+    <t>0.9890,0.0016,0.0002,0.0029</t>
+  </si>
+  <si>
+    <t>0.9933,0.0009,0.0006,0.0017</t>
+  </si>
+  <si>
+    <t>0.9804,0.0083,0.0069,0.0017</t>
+  </si>
+  <si>
+    <t>0.9903,0.0021,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9835,0.0066,0.0031,0.0016</t>
+  </si>
+  <si>
+    <t>0.0163,0.4128,0.8656,0.0040</t>
+  </si>
+  <si>
+    <t>0.0011,0.7842,0.9186,0.0001</t>
+  </si>
+  <si>
+    <t>0.0146,0.2126,0.9109,0.0025</t>
+  </si>
+  <si>
+    <t>0.0055,0.4169,0.9061,0.0015</t>
+  </si>
+  <si>
+    <t>0.7978,0.0233,0.1033,0.0583</t>
+  </si>
+  <si>
+    <t>0.7923,0.0419,0.1766,0.0233</t>
+  </si>
+  <si>
+    <t>0.3289,0.0024,0.8195,0.0112</t>
+  </si>
+  <si>
+    <t>0.6974,0.0361,0.3564,0.0194</t>
+  </si>
+  <si>
+    <t>0.2571,0.0073,0.0032,0.8794</t>
+  </si>
+  <si>
+    <t>0.0007,0.0015,0.0017,0.9991</t>
+  </si>
+  <si>
+    <t>0.0164,0.0079,0.0186,0.9804</t>
+  </si>
+  <si>
+    <t>0.0070,0.0003,0.0085,0.9925</t>
+  </si>
+  <si>
+    <t>0.0081,0.7944,0.7733,0.0019</t>
+  </si>
+  <si>
+    <t>0.9671,0.0356,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.2447,0.7966,0.0174,0.0082</t>
+  </si>
+  <si>
+    <t>0.9194,0.0802,0.0015,0.0041</t>
+  </si>
+  <si>
+    <t>0.9523,0.0376,0.0066,0.0026</t>
+  </si>
+  <si>
+    <t>0.9523,0.0015,0.0011,0.0408</t>
+  </si>
+  <si>
+    <t>0.0860,0.0046,0.0127,0.9553</t>
+  </si>
+  <si>
+    <t>0.9336,0.0124,0.0094,0.0245</t>
+  </si>
+  <si>
+    <t>0.0038,0.1089,0.9662,0.0093</t>
+  </si>
+  <si>
+    <t>0.6389,0.0003,0.0478,0.1305</t>
+  </si>
+  <si>
+    <t>0.8463,0.0041,0.0343,0.0697</t>
+  </si>
+  <si>
+    <t>0.6021,0.3033,0.1556,0.0233</t>
+  </si>
+  <si>
+    <t>0.6082,0.4617,0.0052,0.0103</t>
+  </si>
+  <si>
+    <t>0.7320,0.1580,0.1585,0.0038</t>
+  </si>
+  <si>
+    <t>0.7324,0.2634,0.0160,0.0114</t>
+  </si>
+  <si>
+    <t>0.7295,0.2806,0.0302,0.0026</t>
+  </si>
+  <si>
+    <t>0.8800,0.1064,0.0299,0.0054</t>
+  </si>
+  <si>
+    <t>0.9869,0.0021,0.0010,0.0033</t>
+  </si>
+  <si>
+    <t>0.9765,0.0031,0.0013,0.0091</t>
+  </si>
+  <si>
+    <t>0.9924,0.0023,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9704,0.0016,0.0003,0.0204</t>
+  </si>
+  <si>
+    <t>0.9895,0.0016,0.0010,0.0025</t>
+  </si>
+  <si>
+    <t>0.9850,0.0090,0.0008,0.0010</t>
+  </si>
+  <si>
+    <t>0.9721,0.0013,0.0002,0.0191</t>
+  </si>
+  <si>
+    <t>0.9879,0.0021,0.0005,0.0029</t>
+  </si>
+  <si>
+    <t>0.3544,0.7230,0.0190,0.0080</t>
+  </si>
+  <si>
+    <t>0.5807,0.5741,0.0046,0.0016</t>
+  </si>
+  <si>
+    <t>0.6750,0.4210,0.0154,0.0008</t>
+  </si>
+  <si>
+    <t>0.5860,0.2214,0.2441,0.0047</t>
+  </si>
+  <si>
+    <t>0.9162,0.0834,0.0014,0.0034</t>
+  </si>
+  <si>
+    <t>0.9391,0.0410,0.0152,0.0029</t>
+  </si>
+  <si>
+    <t>0.9688,0.0175,0.0104,0.0014</t>
+  </si>
+  <si>
+    <t>0.9655,0.0179,0.0029,0.0033</t>
+  </si>
+  <si>
+    <t>0.0024,0.0512,0.9945,0.0002</t>
+  </si>
+  <si>
+    <t>0.9297,0.0452,0.0124,0.0069</t>
+  </si>
+  <si>
+    <t>0.0031,0.0045,0.9950,0.0004</t>
+  </si>
+  <si>
+    <t>0.0260,0.1141,0.9427,0.0134</t>
+  </si>
+  <si>
+    <t>0.0297,0.0021,0.9700,0.0182</t>
+  </si>
+  <si>
+    <t>0.0364,0.4027,0.6083,0.0006</t>
+  </si>
+  <si>
+    <t>0.0033,0.0923,0.9808,0.0005</t>
+  </si>
+  <si>
+    <t>0.0112,0.0006,0.9930,0.0011</t>
+  </si>
+  <si>
+    <t>0.0203,0.0039,0.9850,0.0015</t>
+  </si>
+  <si>
+    <t>0.1630,0.0312,0.8672,0.0090</t>
+  </si>
+  <si>
+    <t>0.1142,0.0476,0.8666,0.0113</t>
+  </si>
+  <si>
+    <t>0.6899,0.0491,0.3969,0.0055</t>
+  </si>
+  <si>
+    <t>0.4084,0.0326,0.6779,0.0024</t>
+  </si>
+  <si>
+    <t>0.0702,0.8057,0.2679,0.0101</t>
+  </si>
+  <si>
+    <t>0.3596,0.0511,0.6811,0.0245</t>
+  </si>
+  <si>
+    <t>0.7766,0.0415,0.1046,0.0344</t>
+  </si>
+  <si>
+    <t>0.2186,0.0407,0.8052,0.0315</t>
+  </si>
+  <si>
+    <t>0.7486,0.3374,0.0104,0.0008</t>
+  </si>
+  <si>
+    <t>0.6946,0.3765,0.0144,0.0008</t>
+  </si>
+  <si>
+    <t>0.8480,0.1437,0.0418,0.0030</t>
+  </si>
+  <si>
+    <t>0.9145,0.1301,0.0050,0.0018</t>
+  </si>
+  <si>
+    <t>0.9749,0.0349,0.0015,0.0004</t>
+  </si>
+  <si>
+    <t>0.7717,0.0436,0.2221,0.0127</t>
+  </si>
+  <si>
+    <t>0.7962,0.0141,0.0733,0.0955</t>
+  </si>
+  <si>
+    <t>0.8714,0.0044,0.0496,0.0340</t>
+  </si>
+  <si>
+    <t>0.8127,0.0303,0.2091,0.0086</t>
+  </si>
+  <si>
+    <t>0.6482,0.0402,0.4047,0.0214</t>
+  </si>
+  <si>
+    <t>0.0054,0.0116,0.9801,0.0193</t>
+  </si>
+  <si>
+    <t>0.0127,0.5291,0.8347,0.0062</t>
+  </si>
+  <si>
+    <t>0.0105,0.1873,0.9222,0.0187</t>
+  </si>
+  <si>
+    <t>0.0556,0.0362,0.9165,0.0130</t>
+  </si>
+  <si>
+    <t>0.0223,0.7146,0.4211,0.0050</t>
+  </si>
+  <si>
+    <t>0.9892,0.0056,0.0005,0.0007</t>
   </si>
   <si>
     <t>0.9923,0.0017,0.0002,0.0011</t>
   </si>
   <si>
-    <t>0.9610,0.0271,0.0031,0.0029</t>
-  </si>
-  <si>
-    <t>0.9878,0.0115,0.0009,0.0003</t>
-  </si>
-  <si>
-    <t>0.9964,0.0011,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0014,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9963,0.0010,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9972,0.0008,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9927,0.0024,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.9898,0.0067,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9957,0.0014,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9939,0.0009,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.0180,0.0028,0.9798,0.0081</t>
-  </si>
-  <si>
-    <t>0.0437,0.0088,0.9357,0.0372</t>
-  </si>
-  <si>
-    <t>0.7796,0.0134,0.1449,0.0563</t>
-  </si>
-  <si>
-    <t>0.5112,0.0102,0.6891,0.0032</t>
-  </si>
-  <si>
-    <t>0.1376,0.8532,0.0203,0.0014</t>
-  </si>
-  <si>
-    <t>0.2834,0.8099,0.0037,0.0012</t>
-  </si>
-  <si>
-    <t>0.3255,0.7399,0.0018,0.0040</t>
-  </si>
-  <si>
-    <t>0.1337,0.8559,0.0012,0.0056</t>
-  </si>
-  <si>
-    <t>0.0383,0.9468,0.0026,0.0027</t>
-  </si>
-  <si>
-    <t>0.0410,0.9540,0.0015,0.0009</t>
-  </si>
-  <si>
-    <t>0.8325,0.2558,0.0035,0.0010</t>
-  </si>
-  <si>
-    <t>0.4970,0.1368,0.4672,0.0280</t>
-  </si>
-  <si>
-    <t>0.2384,0.0309,0.7710,0.0040</t>
-  </si>
-  <si>
-    <t>0.4795,0.2047,0.3253,0.0232</t>
-  </si>
-  <si>
-    <t>0.6384,0.0521,0.4651,0.0097</t>
-  </si>
-  <si>
-    <t>0.3773,0.2054,0.1333,0.4620</t>
-  </si>
-  <si>
-    <t>0.0061,0.9762,0.0329,0.0048</t>
-  </si>
-  <si>
-    <t>0.0063,0.9639,0.0083,0.0440</t>
-  </si>
-  <si>
-    <t>0.0284,0.7963,0.0087,0.5471</t>
-  </si>
-  <si>
-    <t>0.0012,0.8512,0.9545,0.0007</t>
-  </si>
-  <si>
-    <t>0.1372,0.8615,0.0416,0.0004</t>
-  </si>
-  <si>
-    <t>0.6390,0.4321,0.0236,0.0016</t>
-  </si>
-  <si>
-    <t>0.4865,0.6659,0.0069,0.0006</t>
-  </si>
-  <si>
-    <t>0.9814,0.0148,0.0018,0.0008</t>
-  </si>
-  <si>
-    <t>0.9865,0.0021,0.0007,0.0032</t>
-  </si>
-  <si>
-    <t>0.9925,0.0011,0.0001,0.0013</t>
-  </si>
-  <si>
-    <t>0.9734,0.0031,0.0008,0.0117</t>
-  </si>
-  <si>
-    <t>0.9844,0.0118,0.0018,0.0006</t>
-  </si>
-  <si>
-    <t>0.9514,0.0173,0.0348,0.0007</t>
-  </si>
-  <si>
-    <t>0.9915,0.0013,0.0011,0.0013</t>
-  </si>
-  <si>
-    <t>0.9704,0.0057,0.0023,0.0085</t>
-  </si>
-  <si>
-    <t>0.0104,0.8038,0.7824,0.0104</t>
-  </si>
-  <si>
-    <t>0.0026,0.6570,0.9376,0.0003</t>
-  </si>
-  <si>
-    <t>0.0326,0.2202,0.8868,0.0150</t>
-  </si>
-  <si>
-    <t>0.0771,0.3893,0.6027,0.0116</t>
-  </si>
-  <si>
-    <t>0.9676,0.0063,0.0182,0.0015</t>
-  </si>
-  <si>
-    <t>0.5851,0.2417,0.0592,0.1140</t>
-  </si>
-  <si>
-    <t>0.3343,0.0086,0.7833,0.0233</t>
-  </si>
-  <si>
-    <t>0.7207,0.1360,0.1092,0.0247</t>
-  </si>
-  <si>
-    <t>0.0286,0.0028,0.0068,0.9813</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.0012,0.9994</t>
-  </si>
-  <si>
-    <t>0.0024,0.0023,0.0036,0.9974</t>
-  </si>
-  <si>
-    <t>0.0136,0.0007,0.0011,0.9945</t>
-  </si>
-  <si>
-    <t>0.0049,0.9014,0.4556,0.0029</t>
-  </si>
-  <si>
-    <t>0.9819,0.0028,0.0007,0.0043</t>
-  </si>
-  <si>
-    <t>0.7503,0.3298,0.0081,0.0042</t>
-  </si>
-  <si>
-    <t>0.9549,0.0236,0.0087,0.0054</t>
-  </si>
-  <si>
-    <t>0.8311,0.1866,0.0269,0.0046</t>
-  </si>
-  <si>
-    <t>0.9771,0.0041,0.0050,0.0049</t>
-  </si>
-  <si>
-    <t>0.4037,0.0085,0.0146,0.6957</t>
-  </si>
-  <si>
-    <t>0.9346,0.0074,0.0032,0.0339</t>
-  </si>
-  <si>
-    <t>0.0017,0.1260,0.9698,0.0147</t>
-  </si>
-  <si>
-    <t>0.6462,0.0013,0.0062,0.4720</t>
-  </si>
-  <si>
-    <t>0.9412,0.0021,0.0215,0.0155</t>
-  </si>
-  <si>
-    <t>0.4942,0.5025,0.1290,0.0365</t>
-  </si>
-  <si>
-    <t>0.7710,0.1701,0.0239,0.0265</t>
-  </si>
-  <si>
-    <t>0.9093,0.0584,0.0294,0.0029</t>
-  </si>
-  <si>
-    <t>0.4178,0.4155,0.2425,0.0402</t>
-  </si>
-  <si>
-    <t>0.6842,0.1971,0.1795,0.0177</t>
-  </si>
-  <si>
-    <t>0.7861,0.2398,0.0190,0.0044</t>
-  </si>
-  <si>
-    <t>0.9914,0.0018,0.0006,0.0013</t>
-  </si>
-  <si>
-    <t>0.9805,0.0094,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9893,0.0008,0.0004,0.0043</t>
-  </si>
-  <si>
-    <t>0.9863,0.0010,0.0007,0.0061</t>
-  </si>
-  <si>
-    <t>0.9700,0.0107,0.0087,0.0030</t>
-  </si>
-  <si>
-    <t>0.9696,0.0286,0.0039,0.0008</t>
-  </si>
-  <si>
-    <t>0.9869,0.0011,0.0003,0.0048</t>
-  </si>
-  <si>
-    <t>0.9924,0.0017,0.0004,0.0010</t>
-  </si>
-  <si>
-    <t>0.2124,0.7987,0.0094,0.0074</t>
-  </si>
-  <si>
-    <t>0.5849,0.4780,0.0255,0.0017</t>
-  </si>
-  <si>
-    <t>0.5186,0.6029,0.0080,0.0007</t>
-  </si>
-  <si>
-    <t>0.7269,0.0232,0.3565,0.0126</t>
-  </si>
-  <si>
-    <t>0.8248,0.2534,0.0056,0.0019</t>
-  </si>
-  <si>
-    <t>0.9552,0.0404,0.0080,0.0019</t>
-  </si>
-  <si>
-    <t>0.9666,0.0257,0.0057,0.0013</t>
-  </si>
-  <si>
-    <t>0.8470,0.1476,0.0041,0.0036</t>
-  </si>
-  <si>
-    <t>0.0093,0.1135,0.9784,0.0009</t>
-  </si>
-  <si>
-    <t>0.9082,0.1011,0.0097,0.0021</t>
-  </si>
-  <si>
-    <t>0.0078,0.0041,0.9907,0.0012</t>
-  </si>
-  <si>
-    <t>0.0146,0.0486,0.9568,0.0137</t>
-  </si>
-  <si>
-    <t>0.0169,0.0042,0.9803,0.0079</t>
-  </si>
-  <si>
-    <t>0.0268,0.0686,0.9495,0.0075</t>
-  </si>
-  <si>
-    <t>0.0185,0.0173,0.9753,0.0013</t>
-  </si>
-  <si>
-    <t>0.0045,0.0024,0.9938,0.0005</t>
-  </si>
-  <si>
-    <t>0.0080,0.0044,0.9906,0.0011</t>
-  </si>
-  <si>
-    <t>0.1049,0.0153,0.9191,0.0040</t>
-  </si>
-  <si>
-    <t>0.1950,0.0565,0.8055,0.0053</t>
-  </si>
-  <si>
-    <t>0.7096,0.0455,0.3303,0.0059</t>
-  </si>
-  <si>
-    <t>0.6828,0.0655,0.3302,0.0119</t>
-  </si>
-  <si>
-    <t>0.2589,0.0680,0.7547,0.0077</t>
-  </si>
-  <si>
-    <t>0.7266,0.0233,0.3613,0.0092</t>
-  </si>
-  <si>
-    <t>0.7088,0.0848,0.2211,0.0184</t>
-  </si>
-  <si>
-    <t>0.3134,0.0174,0.8178,0.0038</t>
-  </si>
-  <si>
-    <t>0.7310,0.3571,0.0116,0.0011</t>
-  </si>
-  <si>
-    <t>0.8635,0.1836,0.0090,0.0013</t>
-  </si>
-  <si>
-    <t>0.9251,0.0917,0.0107,0.0012</t>
-  </si>
-  <si>
-    <t>0.9614,0.0529,0.0019,0.0006</t>
-  </si>
-  <si>
-    <t>0.9853,0.0147,0.0009,0.0004</t>
-  </si>
-  <si>
-    <t>0.7914,0.0654,0.1435,0.0346</t>
-  </si>
-  <si>
-    <t>0.6575,0.1109,0.3018,0.0139</t>
-  </si>
-  <si>
-    <t>0.9021,0.0071,0.0391,0.0251</t>
-  </si>
-  <si>
-    <t>0.8166,0.0524,0.1139,0.0327</t>
-  </si>
-  <si>
-    <t>0.3545,0.0066,0.7846,0.0166</t>
-  </si>
-  <si>
-    <t>0.0414,0.0162,0.9501,0.0171</t>
-  </si>
-  <si>
-    <t>0.1177,0.1485,0.6553,0.1811</t>
-  </si>
-  <si>
-    <t>0.0097,0.0718,0.9434,0.0035</t>
-  </si>
-  <si>
-    <t>0.0478,0.0498,0.8372,0.0981</t>
-  </si>
-  <si>
-    <t>0.0286,0.0907,0.8960,0.0112</t>
-  </si>
-  <si>
-    <t>0.9861,0.0038,0.0001,0.0017</t>
-  </si>
-  <si>
-    <t>0.9838,0.0105,0.0013,0.0010</t>
-  </si>
-  <si>
-    <t>0.9897,0.0037,0.0011,0.0010</t>
-  </si>
-  <si>
-    <t>0.9877,0.0108,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9881,0.0036,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.9916,0.0023,0.0003,0.0009</t>
-  </si>
-  <si>
-    <t>0.9911,0.0035,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9876,0.0042,0.0010,0.0013</t>
-  </si>
-  <si>
-    <t>0.0421,0.0135,0.9597,0.0053</t>
-  </si>
-  <si>
-    <t>0.1478,0.0709,0.8470,0.0067</t>
-  </si>
-  <si>
-    <t>0.8121,0.0836,0.0673,0.0345</t>
-  </si>
-  <si>
-    <t>0.0060,0.0134,0.9864,0.0006</t>
-  </si>
-  <si>
-    <t>0.0012,0.0040,0.9965,0.0014</t>
-  </si>
-  <si>
-    <t>0.0615,0.0834,0.8458,0.0034</t>
-  </si>
-  <si>
-    <t>0.0086,0.0068,0.9896,0.0019</t>
-  </si>
-  <si>
-    <t>0.1091,0.0216,0.8486,0.0884</t>
-  </si>
-  <si>
-    <t>0.0009,0.0023,0.9970,0.0012</t>
-  </si>
-  <si>
-    <t>0.0102,0.0125,0.9512,0.0454</t>
-  </si>
-  <si>
-    <t>0.2189,0.0333,0.8361,0.0149</t>
-  </si>
-  <si>
-    <t>0.6240,0.0045,0.5645,0.0085</t>
-  </si>
-  <si>
-    <t>0.4175,0.0030,0.7302,0.0198</t>
-  </si>
-  <si>
-    <t>0.8928,0.0090,0.0960,0.0089</t>
-  </si>
-  <si>
-    <t>0.9911,0.0029,0.0001,0.0009</t>
-  </si>
-  <si>
-    <t>0.9913,0.0053,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9928,0.0032,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9837,0.0129,0.0040,0.0005</t>
-  </si>
-  <si>
-    <t>0.9842,0.0052,0.0009,0.0018</t>
-  </si>
-  <si>
-    <t>0.9920,0.0053,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9859,0.0088,0.0014,0.0007</t>
-  </si>
-  <si>
-    <t>0.9841,0.0053,0.0027,0.0021</t>
-  </si>
-  <si>
-    <t>0.0384,0.0206,0.9452,0.0068</t>
-  </si>
-  <si>
-    <t>0.0075,0.0361,0.9788,0.0021</t>
-  </si>
-  <si>
-    <t>0.0087,0.1667,0.9515,0.0113</t>
-  </si>
-  <si>
-    <t>0.1478,0.0556,0.7988,0.0094</t>
-  </si>
-  <si>
-    <t>0.0049,0.0032,0.9880,0.0078</t>
-  </si>
-  <si>
-    <t>0.2800,0.0327,0.3989,0.3213</t>
-  </si>
-  <si>
-    <t>0.2631,0.0023,0.7019,0.0432</t>
-  </si>
-  <si>
-    <t>0.0026,0.0055,0.7881,0.6615</t>
-  </si>
-  <si>
-    <t>0.7883,0.0012,0.0148,0.1912</t>
-  </si>
-  <si>
-    <t>0.0242,0.0024,0.0016,0.9900</t>
-  </si>
-  <si>
-    <t>0.0371,0.0032,0.0065,0.9811</t>
-  </si>
-  <si>
-    <t>0.0029,0.0001,0.0002,0.9989</t>
-  </si>
-  <si>
-    <t>0.0026,0.0006,0.0016,0.9979</t>
-  </si>
-  <si>
-    <t>0.6081,0.0404,0.1310,0.3136</t>
+    <t>0.9921,0.0030,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9918,0.0046,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9910,0.0024,0.0002,0.0012</t>
+  </si>
+  <si>
+    <t>0.9872,0.0031,0.0005,0.0018</t>
+  </si>
+  <si>
+    <t>0.9939,0.0026,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9796,0.0075,0.0062,0.0021</t>
+  </si>
+  <si>
+    <t>0.0754,0.0138,0.9519,0.0014</t>
+  </si>
+  <si>
+    <t>0.1562,0.2130,0.7454,0.0097</t>
+  </si>
+  <si>
+    <t>0.8233,0.0115,0.0313,0.1048</t>
+  </si>
+  <si>
+    <t>0.0073,0.0282,0.9761,0.0063</t>
+  </si>
+  <si>
+    <t>0.0003,0.0946,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.0335,0.3373,0.6992,0.0052</t>
+  </si>
+  <si>
+    <t>0.0010,0.0015,0.9957,0.0033</t>
+  </si>
+  <si>
+    <t>0.0233,0.0055,0.9707,0.0086</t>
+  </si>
+  <si>
+    <t>0.0015,0.0077,0.9934,0.0008</t>
+  </si>
+  <si>
+    <t>0.0383,0.0471,0.7941,0.1637</t>
+  </si>
+  <si>
+    <t>0.1620,0.0468,0.8348,0.0035</t>
+  </si>
+  <si>
+    <t>0.7798,0.0070,0.0882,0.0964</t>
+  </si>
+  <si>
+    <t>0.6185,0.0052,0.3430,0.0461</t>
+  </si>
+  <si>
+    <t>0.5562,0.0060,0.3583,0.0823</t>
+  </si>
+  <si>
+    <t>0.9954,0.0019,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9947,0.0020,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9954,0.0015,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9825,0.0223,0.0012,0.0002</t>
+  </si>
+  <si>
+    <t>0.9822,0.0017,0.0004,0.0076</t>
+  </si>
+  <si>
+    <t>0.9927,0.0047,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9956,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9817,0.0058,0.0008,0.0029</t>
+  </si>
+  <si>
+    <t>0.0558,0.0315,0.9468,0.0045</t>
+  </si>
+  <si>
+    <t>0.0018,0.0140,0.9905,0.0026</t>
+  </si>
+  <si>
+    <t>0.0196,0.0036,0.9761,0.0062</t>
+  </si>
+  <si>
+    <t>0.0354,0.0096,0.9597,0.0011</t>
+  </si>
+  <si>
+    <t>0.0023,0.0021,0.9919,0.0058</t>
+  </si>
+  <si>
+    <t>0.0459,0.0041,0.8822,0.1651</t>
+  </si>
+  <si>
+    <t>0.0258,0.0101,0.9643,0.0031</t>
+  </si>
+  <si>
+    <t>0.0055,0.0011,0.9672,0.0957</t>
+  </si>
+  <si>
+    <t>0.4870,0.0007,0.0197,0.5146</t>
+  </si>
+  <si>
+    <t>0.0121,0.0265,0.0022,0.9919</t>
+  </si>
+  <si>
+    <t>0.0763,0.0049,0.0024,0.9715</t>
+  </si>
+  <si>
+    <t>0.0024,0.0002,0.0087,0.9948</t>
+  </si>
+  <si>
+    <t>0.0019,0.0001,0.0013,0.9985</t>
+  </si>
+  <si>
+    <t>0.3102,0.0471,0.0073,0.7778</t>
   </si>
 </sst>
 </file>
@@ -1962,7 +1968,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1976,7 +1982,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1987,10 +1993,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2004,7 +2010,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2018,7 +2024,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2032,7 +2038,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2046,7 +2052,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2060,7 +2066,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2074,7 +2080,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2088,7 +2094,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2102,7 +2108,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2116,7 +2122,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2130,7 +2136,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2144,7 +2150,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2158,7 +2164,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2172,7 +2178,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2186,7 +2192,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2200,7 +2206,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2214,7 +2220,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2225,10 +2231,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D21" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2242,7 +2248,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2256,7 +2262,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2267,10 +2273,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D24" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2281,10 +2287,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="D25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2298,7 +2304,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2312,7 +2318,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2326,7 +2332,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2340,7 +2346,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2354,7 +2360,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2365,10 +2371,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2379,10 +2385,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D32" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2396,7 +2402,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2410,7 +2416,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2421,10 +2427,10 @@
         <v>259</v>
       </c>
       <c r="C35" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D35" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2435,10 +2441,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2449,10 +2455,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D37" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2466,7 +2472,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2477,10 +2483,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2494,7 +2500,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2508,7 +2514,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2522,7 +2528,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2536,7 +2542,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2550,7 +2556,7 @@
         <v>263</v>
       </c>
       <c r="D44" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2564,7 +2570,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2575,10 +2581,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2592,7 +2598,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2606,7 +2612,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2620,7 +2626,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2634,7 +2640,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2645,10 +2651,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D51" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2662,7 +2668,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2676,7 +2682,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2690,7 +2696,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2704,7 +2710,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2718,7 +2724,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2732,7 +2738,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2746,7 +2752,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2760,7 +2766,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2774,7 +2780,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2788,7 +2794,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2802,7 +2808,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2816,7 +2822,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2830,7 +2836,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2844,7 +2850,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2858,7 +2864,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2872,7 +2878,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2886,7 +2892,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2900,7 +2906,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2914,7 +2920,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2928,7 +2934,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2942,7 +2948,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2956,7 +2962,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2970,7 +2976,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2981,10 +2987,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2998,7 +3004,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3012,7 +3018,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3026,7 +3032,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3040,7 +3046,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3054,7 +3060,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3068,7 +3074,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3082,7 +3088,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3096,7 +3102,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3110,7 +3116,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3124,7 +3130,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3138,7 +3144,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3152,7 +3158,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3163,10 +3169,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3180,7 +3186,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3194,7 +3200,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3208,7 +3214,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3222,7 +3228,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3236,7 +3242,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3250,7 +3256,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3264,7 +3270,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3278,7 +3284,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3292,7 +3298,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3306,7 +3312,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3320,7 +3326,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3334,7 +3340,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3348,7 +3354,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3362,7 +3368,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3376,7 +3382,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3390,7 +3396,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3404,7 +3410,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3418,7 +3424,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3432,7 +3438,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3446,7 +3452,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3460,7 +3466,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3474,7 +3480,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3488,7 +3494,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3502,7 +3508,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3516,7 +3522,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3530,7 +3536,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3544,7 +3550,7 @@
         <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3558,7 +3564,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3572,7 +3578,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3586,7 +3592,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3600,7 +3606,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3611,10 +3617,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="D120" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3628,7 +3634,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3642,7 +3648,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3653,10 +3659,10 @@
         <v>262</v>
       </c>
       <c r="C123" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3670,7 +3676,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3684,7 +3690,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3695,10 +3701,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3709,10 +3715,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D127" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3726,7 +3732,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3740,7 +3746,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3754,7 +3760,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3768,7 +3774,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3782,7 +3788,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3796,7 +3802,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3810,7 +3816,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3824,7 +3830,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3835,10 +3841,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3852,7 +3858,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3866,7 +3872,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3880,7 +3886,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3894,7 +3900,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3908,7 +3914,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3922,7 +3928,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3936,7 +3942,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3950,7 +3956,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3964,7 +3970,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3978,7 +3984,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3992,7 +3998,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4003,10 +4009,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4020,7 +4026,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4031,10 +4037,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4048,7 +4054,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4062,7 +4068,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4076,7 +4082,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4090,7 +4096,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4104,7 +4110,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4118,7 +4124,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4132,7 +4138,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4146,7 +4152,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4157,10 +4163,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4174,7 +4180,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4188,7 +4194,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4202,7 +4208,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4216,7 +4222,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4230,7 +4236,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4244,7 +4250,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4258,7 +4264,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4272,7 +4278,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4286,7 +4292,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4300,7 +4306,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4314,7 +4320,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4328,7 +4334,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4342,7 +4348,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4356,7 +4362,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4367,10 +4373,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D174" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4381,10 +4387,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4398,7 +4404,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4412,7 +4418,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4426,7 +4432,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4440,7 +4446,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4454,7 +4460,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4468,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4482,7 +4488,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4496,7 +4502,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4510,7 +4516,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4524,7 +4530,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4538,7 +4544,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4552,7 +4558,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4566,7 +4572,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4580,7 +4586,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4594,7 +4600,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4608,7 +4614,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4622,7 +4628,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4633,10 +4639,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4647,10 +4653,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D194" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4661,10 +4667,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4678,7 +4684,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4692,7 +4698,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4706,7 +4712,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4720,7 +4726,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4734,7 +4740,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4748,7 +4754,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4762,7 +4768,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4776,7 +4782,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4790,7 +4796,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4804,7 +4810,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4818,7 +4824,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4829,10 +4835,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4846,7 +4852,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4857,10 +4863,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D209" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4874,7 +4880,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4888,7 +4894,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4899,10 +4905,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D212" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4916,7 +4922,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4930,7 +4936,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4944,7 +4950,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4958,7 +4964,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4972,7 +4978,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4986,7 +4992,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -5000,7 +5006,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5014,7 +5020,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5028,7 +5034,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5042,7 +5048,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5056,7 +5062,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5070,7 +5076,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5084,7 +5090,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5098,7 +5104,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5112,7 +5118,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5126,7 +5132,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5140,7 +5146,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5154,7 +5160,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5168,7 +5174,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5179,10 +5185,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5193,10 +5199,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5210,7 +5216,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5224,7 +5230,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5238,7 +5244,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5252,7 +5258,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5266,7 +5272,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5280,7 +5286,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5294,7 +5300,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5308,7 +5314,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5322,7 +5328,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5336,7 +5342,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5350,7 +5356,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5364,7 +5370,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5378,7 +5384,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5392,7 +5398,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5403,10 +5409,10 @@
         <v>261</v>
       </c>
       <c r="C248" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5420,7 +5426,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5431,10 +5437,10 @@
         <v>261</v>
       </c>
       <c r="C250" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5445,10 +5451,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5462,7 +5468,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5476,7 +5482,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5490,7 +5496,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5504,7 +5510,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5515,10 +5521,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
